--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_010/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_010/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -470,6 +475,11 @@
       </text>
     </comment>
     <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1311,12 +1321,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Steady RANS prediction of CL, CD, and Cp for NASA CRM wing-body at M≈0.85, Re≈5M, α∈[1°,4°] to support preliminary aero-loads and trim analyses</t>
+          <t>Steady RANS CFD predictions of CL, CD, and Cp for NASA CRM wing-body at transonic cruise (M≈0.85, Re≈5M, α∈[1°,4°]) to support preliminary aero-loads and trim analyses</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>FUN3D v13.2 SA-neg RANS computations on three systematically refined unstructured meshes are assessed for their ability to bound lift-curve slope, zero-lift drag, and pitching moment for the NASA Common Research Model wing-body in transonic cruise. Outputs feed a performance workbook update and early control-surface margin assessment. Scope excludes buffet, aeroelastic deformation, transition modeling, and high-lift.</t>
+          <t>FUN3D v13.2 SA-neg RANS simulations of the NASA Common Research Model wing-body configuration at M=0.85, Re=5×10^6, angles of attack 1°–4°. Results are intended to update lift-curve slope and zero-lift drag inputs in a performance workbook and to bound pitching moment for control surface margin assessment. Scope is limited to rigid geometry, fully turbulent, steady-state flow. Buffet, aeroelastic deformation, high-lift, and unsteady phenomena are explicitly excluded.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1354,9 +1364,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md; appendix.md (CRM Wing-Body Transonic Aerodynamics CFD Credibility Assessment Report, dated 2026-08-06)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1475,7 +1485,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>CL and CD Accuracy Requirement for Performance Workbook</t>
+          <t>Decision-quality CL and CD at M≈0.85, Re≈5M for preliminary loads and trim</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1485,7 +1495,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>CFD predictions of CL and CD at M=0.85, Re=5M, α=2°–4° must be consistent with NASA NTF wind tunnel data within traceable uncertainty bands sufficient to bound lift-curve slope and zero-lift drag inputs for preliminary trim and fuel burn sensitivity analyses.</t>
+          <t>Model must predict CL within acceptable accuracy and CD within bounded uncertainty to support performance workbook updates and pitching moment bounds for control surface margin assessment at the specified cruise conditions</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1512,7 +1522,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Density-based, second-order Roe/HLLE compressible RANS solver with Spalart-Allmaras negative viscosity fix turbulence model; select runs with k-ω SST for sensitivity; run on three unstructured meshes (C1 1.3M, C2 5.1M, C3 20.7M cells).</t>
+          <t>Density-based, second-order Roe/HLLE, Spalart-Allmaras with negative viscosity fix RANS solver applied to the NASA CRM wing-body on three systematically refined unstructured meshes (1.3M, 5.1M, 20.7M cells)</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1539,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Measured CL, CD, Cm, and surface Cp distributions for the NASA Common Research Model wing-body at M=0.85, Re=5M from the National Transonic Facility; Run IDs NTF-CRM-TX-085-05 to -09; used as the validation comparator.</t>
+          <t>Measured CL, CD, Cm, and surface Cp for the NASA Common Research Model at M=0.85, Re=5M from the National Transonic Facility; run IDs NTF-CRM-TX-085-05 to -09; used as the primary validation comparator</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1551,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>CRM Baseline CAD Geometry</t>
+          <t>NASA CRM Wing-Body Geometry (CAD rev CRM-WB-2010-05)</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>NASA CRM wing-body baseline geometry (fuselage and symmetric wing, no twist modifications) used as the rigid computational geometry for all simulations.</t>
+          <t>Public-repository baseline CAD geometry for the CRM wing-body fuselage and symmetric wing, used without twist modification or aeroelastic deformation</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1993,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Grid Convergence Study (CL and CD)</t>
+          <t>Grid convergence study — CL and CD</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1998,12 +2008,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Three systematically refined meshes (C1 1.3M, C2 5.1M, C3 20.7M cells) were run at M=0.85, Re=5M, α=3° with SA-neg. Monotonic convergence observed; Richardson extrapolation performed assuming observed order p≈1.8. Extrapolated CL∞≈0.540 (grid half-width ±0.002); extrapolated CD∞≈0.02763 (grid half-width ±4 counts).</t>
+          <t>Three-level mesh refinement (C1: 1.3M, C2: 5.1M, C3: 20.7M cells) at M=0.85, Re=5M, α=3°. Observed convergence order p≈1.8 (sub-quadratic, consistent with mixed-element grids). Richardson extrapolation performed to estimate grid-converged values.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Richardson-extrapolated continuum limit</t>
+          <t>Extrapolated grid-converged values CL∞≈0.540, CD∞≈0.02763</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2013,12 +2023,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Richardson extrapolation with observed order p≈1.8</t>
+          <t>Richardson extrapolation with observed order p≈1.8; estimated grid half-widths: CL ±0.002, CD ±4 counts</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>CL grid half-width ±0.002; CD grid half-width ±4 drag counts; shock location shift 0.7% MAC between C2 and C3</t>
+          <t>CL monotone: 0.529→0.536→0.538; CD monotone: 0.02692→0.02738→0.02753; shock position shift C2→C3: ~0.7% MAC at η=0.7</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2030,7 +2040,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Integrated Force Comparison Against NTF Data</t>
+          <t>Integrated force comparison vs NASA NTF data (CL, CD, Cm)</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2040,12 +2050,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>C3 SA-neg predictions of CL, CD, and Cm compared point-by-point against NASA NTF measurements at α=2°, 3°, 4°, M=0.85, Re=5M.</t>
+          <t>Point-by-point comparison of C3 SA-neg predictions against NASA NTF balance measurements at α=2°, 3°, 4°, M=0.85, Re=5M for CL, CD, and Cm about quarter-MAC</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>NASA NTF CRM wind tunnel measurements (TM-2010-216807)</t>
+          <t>NASA NTF CRM wind tunnel measurements (NASA TM-2010-216807)</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2055,12 +2065,12 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>Quadrature combination of numerical resolution, input variability (α ±0.02°, M ±0.0005, Re ±1%), and turbulence model proxy; 95% intervals</t>
+          <t>Combined uncertainty budget: numerical resolution (grid trend), input variability (α ±0.02°, M ±0.0005, Re ±1% propagated via local linear sensitivities), and turbulence model proxy (SA-neg vs SST difference reduced 30% at C3); quadrature sum gives 95% intervals</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>CL within +1.1% to +1.2% across α=2°–4°; CD underprediction −1.4 counts (α=2°) to −9.6 counts (α=4°); Cm bias 0.003 at α=3°; combined 95% uncertainty ±1.8% CL, ±9 counts CD at α=3°</t>
+          <t>CL error: +1.1% to +1.2% across α=2°–4°; CD error: −1.4 counts (α=2°) to −9.6 counts (α=4°); Cm bias at α=3°: 0.003 absolute; 95% UQ bands: CL ±1.8%, CD ±9 counts at α=3°</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2072,7 +2082,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Surface Cp Distribution Comparison</t>
+          <t>Surface pressure distribution comparison vs NTF (Cp)</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2082,22 +2092,27 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Upper-surface Cp distributions at η=0.6, 0.7, 0.8 for α=3° on C3 compared against NTF pressure tap data. Shock location and shape assessed.</t>
+          <t>Wing upper-surface Cp compared at η=0.6, 0.7, 0.8 sections for α=3°, M=0.85, Re=5M between C3 CFD and digitized NTF data. Shock position and Cp magnitude assessed.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>NASA NTF CRM surface Cp measurements</t>
+          <t>NASA NTF digitized Cp distributions (NASA TM-2010-216807; digitization scripts in /data/NTF_CRM)</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>RMS Cp difference computed over 0.2 ≤ x/c ≤ 0.8; shock location offset assessed as fraction of MAC</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>RMS Cp mismatch 0.034 over 0.2≤x/c≤0.8; CFD shock at x/c≈0.46–0.49 vs WT 0.47–0.50 (≤2% MAC bias); lower surface within 0.01 absolute</t>
+          <t>RMS Cp delta ≈ 0.034 (dominated by shock cell); shock position: CFD x/c≈0.46–0.49 vs WT 0.47–0.50 (bias ≤2% MAC); lower surface Cp within 0.01 absolute</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2109,7 +2124,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Turbulence Model Sensitivity (SA-neg vs SST)</t>
+          <t>Turbulence model sensitivity — SA-neg vs SST on C2 at α=3°</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2119,12 +2134,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>SA-neg replaced by k-ω SST on C2 at α=3° to characterize turbulence model form uncertainty contribution to CD and CL; treated as model-form proxy for UQ.</t>
+          <t>Replacement of SA-neg with k-ω SST on the C2 mesh at α=3° to assess turbulence closure sensitivity as a proxy for model-form uncertainty in CD</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>SA-neg baseline on C2</t>
+          <t>SA-neg baseline on C2 and NTF reference CD</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2134,24 +2149,24 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Difference between SA-neg and SST reduced by 30% on C3 to estimate model-form spread; included in quadrature UQ</t>
+          <t>Model-form proxy: SST–SA-neg difference (6 counts CD) reduced 30% at C3 level; used as turbulence-model spread contribution in quadrature UQ</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>SST increases CD by ~6 counts vs SA-neg; CL change −0.2%; model-form CD proxy ±4 counts on C3</t>
+          <t>SST increases CD by ~6 counts vs SA-neg on C2; CL change &lt;0.2%; SST shock marginally thicker</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Inconclusive</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Solver Convergence and Code Health Verification</t>
+          <t>Numerical solver convergence and robustness checks</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2161,12 +2176,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Residuals dropped ≥5 orders and force monitors flattened to within ±0.2 counts over final 2000 iterations for all meshes and α. FUN3D regression suite executed on the same cluster image; manufactured-solution laminar cases confirmed ~2nd-order L2 error reduction for velocity and pressure; inviscid isentropic vortex decay matched expected behavior.</t>
+          <t>Iterative convergence monitoring for all runs; residual drop ≥5 orders, force monitors steady within ±0.2 counts CL over final 2000 iterations. Initial-condition perturbation test to check for multiple steady states. Spot re-run of α=3° C2 for reproducibility.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Analytical manufactured solutions and isentropic vortex benchmark</t>
+          <t>Convergence criteria defined in run matrix (Appendix A1)</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2176,7 +2191,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>Residual drop ≥1e-5; CL monitor steady within 0.0002; CD monitor steady within 0.00004; spot re-run reproducibility CL within 0.05%, CD within 0.3 counts</t>
+          <t>Residuals dropped 5–6 orders; CL monitor steady to ±0.0002; CD monitor steady to ±0.00004; re-run reproducibility: CL within 0.05%, CD within 0.3 counts</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2330,12 +2345,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Evidence of solver testing, version control, and reproducible build environment</t>
+          <t>Evidence of solver verification, regression testing, and build traceability adequate for research-grade aerodynamics use</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>FUN3D v13.2 is a NASA-maintained solver built from a tagged source drop (v13.2) with documented compiler and library versions (Intel oneAPI 2024.0, PETSc 3.18). Runtime containers (Apptainer 1.2) freeze library dependencies with recorded checksums. A FUN3D regression suite was executed on the same cluster image prior to the campaign. Git commit hash (8f6c1d2) and container hash (sha256:7c13f2b...) recorded. Postprocessing scripts are version-pinned. All documented in report.md Sections 4 and 10 and appendix.md A4.</t>
+          <t>FUN3D v13.2 regression suite executed on the same cluster image prior to the campaign. Manufactured-solution laminar cases confirmed ~2nd-order L2 error reduction for velocity and pressure. Inviscid isentropic vortex decay matched expected behavior. Executable built from NASA source drop v13.2 with documented compiler chain (Intel oneAPI 2024.0, PETSc 3.18). Runtime containers (Apptainer 1.2) freeze library dependencies with recorded recipe and checksum. Git commit hash (8f6c1d2) and container hash (sha256:7c13f2b...) recorded. Postprocessing scripts version-pinned via requirements.txt. Spot re-run reproduced results to within 0.05% CL, 0.3 counts CD.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2360,16 +2375,16 @@
         <v>3</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Evidence that FUN3D correctly solves its governing equations via benchmark or manufactured-solution tests</t>
+          <t>Evidence that the solver correctly implements its governing equations via analytical or benchmark solutions</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>A manufactured-solution laminar code health pass confirmed ~2nd-order L2 error reduction for velocity and pressure with the chosen options. An inviscid isentropic vortex decay test matched expected behavior. These tests are acknowledged as limited (not a full physics validation) but reduce risk of broken build. No formal Method of Manufactured Solutions (MMS) campaign beyond the laminar cases was documented. Report.md Section 4.</t>
+          <t>FUN3D regression suite included manufactured-solution laminar cases showing ~2nd-order L2 error reduction in velocity and pressure with chosen spatial discretization options. Inviscid isentropic vortex decay test matched expected theoretical behavior. These code-health checks were run on the identical cluster image used for the campaign. Limitations: MMS was limited to laminar flow; no separate turbulence MMS reported. Nonetheless, evidence of correct second-order implementation is documented.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2398,12 +2413,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence study with quantified grid-induced uncertainty for CL and CD</t>
+          <t>Systematic mesh refinement study with quantified grid-induced uncertainty for the quantities of interest</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three systematically refined meshes (C1 1.3M, C2 5.1M, C3 20.7M) with consistent near-wall spacing (y+&lt;1) were exercised. Monotonic convergence observed for CL and CD. Richardson extrapolation with observed order p≈1.8 yields CL∞≈0.540 (half-width ±0.002) and CD∞≈0.02763 (half-width ±4 counts). Shock location shift of 0.7% MAC between C2 and C3 quantified. Mesh quality metrics (orthogonality, aspect ratio) reported. Grid uncertainty propagated into the combined 95% UQ bands. Report.md Sections 5 and 9; appendix.md A1.</t>
+          <t>Three systematically refined meshes (C1: 1.3M, C2: 5.1M, C3: 20.7M cells) with consistent near-wall spacing (y+&lt;1 maintained across all levels). Monotonic convergence observed for CL and CD at M=0.85, Re=5M, α=3°. Richardson extrapolation performed; observed order p≈1.8 (sub-quadratic, consistent with mixed-element grids). Grid-induced half-widths quantified: CL ±0.002, CD ±4 counts. Shock location shift C2→C3 only 0.7% MAC. Farfield sensitivity (25 vs 15 spans) showed &lt;1 count CD, &lt;0.1% CL change. Cell quality metrics (orthogonality&gt;0.2, AR&lt;1200) checked; no negative volumes.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2432,12 +2447,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residual convergence and force monitor plateau demonstrated for all production runs</t>
+          <t>Evidence that iterative solver converges adequately and that residual plateaus do not drive force errors</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Residuals for continuity and momentum dropped ≥5 orders in all cases. Lift and drag monitors flattened to within ±0.2 counts over the final 2000 iterations. Convergence criteria of residual drop ≥1e-5 and CL steady within 0.0002 / CD within 0.00004 applied across all α and mesh levels. Robustness to initial condition perturbation confirmed (no multiple steady states). Convergence history plots described in appendix.md A2 (Figure A2-4). Report.md Sections 4 and appendix.md A1.</t>
+          <t>Residuals for continuity and momentum reduced by at least 5 orders of magnitude in all runs (5–6 orders observed). Force monitors (CL, CD) plateaued to within ±0.0002 CL and ±0.00004 CD over the final 2000 iterations. Solver residual plateau explicitly checked against force movement and confirmed not to be the dominant error source. Perturbation of initial conditions (zero-lift vs prior-solution start) yielded the same converged branch for all α; no evidence of multiple steady states at M=0.85, α≤4°. Convergence histories plotted (Figure A2-4). ILU(0)/GMRES with multigrid and CFL ramp to 200 documented.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2466,12 +2481,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Evidence that model setup (BCs, geometry, inputs) was correctly implemented and independently checked</t>
+          <t>Evidence of correct model setup including boundary conditions, geometry, and mesh quality verification</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Boundary conditions (M, Re, α, farfield extent, wall treatment) are fully documented and traceable to NTF logbooks. α was corrected for elastic deflection using balance calibrations; both raw and corrected values were compared. Makefile-driven workflow with YAML case descriptors reduces manual error. Spot re-run of α=3° C2 case from a fresh working directory reproduced CL within 0.05% and CD within 0.3 counts, demonstrating reproducibility. Container and script checksums recorded. No explicit independent third-party review of setup is documented. Report.md Sections 3, 6, and 10; appendix.md A4.</t>
+          <t>Boundary conditions documented: O-type farfield at 25 spans, symmetry plane, characteristic farfield outflow, inflow specified by M/α/T from NTF logbooks. CAD geometry identified (rev CRM-WB-2010-05, public repository). Mesh quality metrics reported (orthogonality&gt;0.2, AR&lt;1200, no negative volumes). Postprocessing automated via Makefile/YAML workflow to reduce manual errors. Reproducibility spot-check performed. Wall temperature set to 300 K with documented negligible effect. Gas property sensitivity (Sutherland vs constant Prandtl) checked. No explicit independent third-party review of setup documented; reproducibility check by same group.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2500,12 +2515,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Justification of governing equations, turbulence model selection, and documented limitations</t>
+          <t>Justification of governing equation choices, turbulence model selection, and documented known limitations</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>SA-neg chosen with explicit rationale: widely used for attached/weakly separated transonic wings, computationally efficient for grid sweeps, consistent with NTF fully turbulent test conditions. SST run on C2 at α=3° provides model-form sensitivity. Known limitations are explicitly documented: steady RANS cannot resolve shock-induced separation pockets near outboard wing at higher α; no transition modeling; no aeroelastic deformation; no unsteady phenomena. Drag underprediction attributed to SA-neg tendency in this regime. Report.md Sections 3, 7, 8, 11, and 12.</t>
+          <t>Governing equations: compressible steady RANS documented and justified for attached/weakly separated transonic wing flow. SA-neg selected with explicit rationale (widely used for transonic wings, computationally efficient for grid sweeps). k-ω SST run as sensitivity. Fully turbulent assumption justified by NTF test practice of forced transition. Known limitations explicitly documented: no buffet/unsteadiness, no aeroelastic coupling, no transition modeling, steady RANS under-resolves shock-induced separation near outboard wing at α=4°, drag partitioning unreliable. Turbulence model identified as dominant source of CD uncertainty. Limitation of single solver family noted.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2530,16 +2545,16 @@
         <v>3</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Input data (M, Re, α, geometry) well-characterized with uncertainties</t>
+          <t>Input parameters accurately characterized with uncertainty bounds derived from measurement sources</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>M, Re, and α drawn from NTF test logbooks with stated uncertainties (M ±0.0005, Re ±1%, α ±0.02°). α corrected for sting effects and elastic deflection using balance calibrations. Gas properties set to dry air γ=1.4; Sutherland vs constant Prandtl sensitivity checked (negligible effect). Wall roughness not included based on reported hydraulically smooth surface. CAD geometry from public CRM repository (rev CRM-WB-2010-05). Input uncertainties propagated into UQ bands via local linear sensitivities. Report.md Sections 3, 6, and 9.</t>
+          <t>Mach number from NTF tunnel logbooks with total-temperature drift correction; variability ±0.0005 quantified. Reynolds number based on reference chord at 25% MAC; uncertainty ±1% from facility data reduction. Angle of attack balance-calibrated with stated uncertainty ±0.02°; both raw and trim-corrected α compared, corrected value used. Sting effect corrections noted and their treatment documented. Gas properties (γ=1.4, dry air) with Sutherland sensitivity check (&lt;1 count CD effect). Surface finish assumed hydraulically smooth per NTF report. Local linear sensitivities computed for all key inputs (∂CL/∂α, ∂CD/∂α, ∂CL/∂M, etc.) via ±1% finite differences with documented re-equilibration (300–500 pseudo-timesteps).</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2568,12 +2583,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Adequate characterization of the experimental test article used as the validation comparator</t>
+          <t>Adequate characterization of experimental test articles used as comparators</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>The NTF CRM dataset (NASA TM-2010-216807) is a well-documented public NASA facility campaign on the canonical CRM wing-body model. Run IDs are cited (NTF-CRM-TX-085-05 to -09). However, the report relies on a single facility and a limited subset of α (2°, 3°, 4°). No information is provided on number of repeat runs, statistical scatter of the WT measurements, or production-representativeness beyond the reference. Balance repeatability of ~±0.5 counts for CD is stated. No cross-facility replication. Report.md Sections 6 and 9.</t>
+          <t>Validation comparator is the NASA CRM wing-body tested at the NTF facility, a well-characterized and widely published reference configuration (Rivers et al., NASA TM-2010-216807; Vassberg et al., AIAA-2008-6919). Run IDs NTF-CRM-TX-085-05 to -09 identified. Integrated forces pulled from tabulated appendices; Cp data digitized from published figures with digitization scripts and calibration notes recorded in /data/NTF_CRM. However, no information is provided on number of repeat runs, balance calibration traceability beyond the ±0.5-count repeatability statement, or specimen/model manufacturing tolerances. Single facility; no multi-facility comparison beyond a recommendation for future work.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2602,12 +2617,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions well-controlled and measurement uncertainties documented</t>
+          <t>Experimental test conditions well-controlled and measured with documented uncertainties</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>NTF conditions (M, Re, α) drawn from facility logbooks with corrections for total temperature drift and sting effects documented. Measurement uncertainties quantified: M ±0.0005, Re ±1%, α ±0.02°, CD balance repeatability ~±0.5 counts. Test was conducted to NASA facility standards at the NTF. Wind tunnel data digitized from NASA TM-2010-216807 with tabulated force appendices used where available; digitization scripts and calibration notes retained. Report.md Section 6; appendix.md A6.</t>
+          <t>NTF test conditions characterized: M, Re, α with stated uncertainties from facility data reduction (M ±0.0005, Re ±1%, α ±0.02°). Balance repeatability for CD stated as ~±0.5 counts. Total-temperature drift correction applied to Mach number. Sting trim corrections documented. Wind tunnel data uncertainties explicitly noted as smaller than CFD prediction intervals, so comparison is CFD-dominated. Test conducted at a NASA facility with implied calibration standards. Limitation: no explicit reference to specific calibration standards (ASTM/ISO) or environmental control documentation in the report.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2636,12 +2651,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Demonstrated matching between CFD input parameters and experimental test conditions</t>
+          <t>Model inputs demonstrably match experimental test conditions with uncertainty propagation</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>CFD inflow conditions (M, Re, α) set to match NTF test logbook values including correction for elastic deflection. Both raw balance α and corrected α were evaluated; corrected value used in production runs. Farfield boundary conditions (characteristic farfield, inflow specified by M, α, static temperature) consistent with NTF conditions. Fully turbulent assumption aligned with NTF forced-transition tests. Gas properties and wall conditions justified against test conditions. Input uncertainties propagated and compared against WT uncertainties. Report.md Sections 3, 6, and 9.</t>
+          <t>CFD inflow conditions (M, Re, α) set to match NTF run conditions using corrected balance α values. Comparison of raw vs corrected α performed; corrected value used to align rigid-body reference with CFD assumption. Fuselage/wing surface finish assumed smooth consistent with NTF report. Temperature set to match NTF conditions (300 K isothermal wall; negligible effect documented). Mach and Re variability propagated into UQ bands. Key mismatch acknowledged: CFD assumes rigid geometry while NTF model has some elastic deformation; sting effects removed from α but their influence on pressure field not corrected. Fully turbulent assumption matched to NTF forced-transition practice.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2670,12 +2685,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of CFD predictions to experimental data with uncertainty bands for all QoIs</t>
+          <t>Quantitative comparison of model predictions to experimental data with error metrics and uncertainty characterization</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Point-by-point comparison of CL, CD, and Cm at α=2°, 3°, 4° on C3: CL within +1.1%–+1.2%; CD underprediction −1.4 to −9.6 counts; Cm bias 0.003. Surface Cp RMS mismatch 0.034; shock location bias ≤2% MAC. Combined 95% uncertainty bands (±1.8% CL, ±9 counts CD at α=3°) computed and compared against WT data; all CL measurements captured within bands; CD at α=4° exceeds bands by ~2 counts, explicitly acknowledged. Lift curve slope within 2% of tunnel slope. Pitching moment trend matched. Report.md Sections 7, 9; appendix.md A2.</t>
+          <t>Point-by-point comparison at three α values (2°, 3°, 4°) for CL, CD, Cm, and Cp distributions. CL errors +1.1%–+1.2%; CD errors −1.4 to −9.6 counts; Cm bias 0.003 absolute at α=3°. RMS Cp mismatch 0.034 over 0.2≤x/c≤0.8; shock position bias ≤2% MAC; lower surface Cp within 0.01 absolute. Lift-curve slope agreement within 2%. Combined 95% uncertainty intervals reported: CL ±1.8%, CD ±9 counts at α=3°. CD at α=4° falls outside the combined interval (~11 counts underprediction vs ±9-count band), explicitly noted as a caveat. Multiple output types and multiple comparison points provided. Trend analysis (slope, systematic bias interpretation) included. Figure descriptions confirm overlaid CFD vs WT plots with error bars.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2700,16 +2715,16 @@
         <v>3</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs (CL, CD, Cm, Cp) are directly relevant to the stated decisions and measurable both computationally and experimentally</t>
+          <t>QoIs directly address the decision requirements and are measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>QoIs (CL, CD, Cm, surface Cp) directly address the two stated decisions: lift curve slope and zero-lift drag for the performance workbook, and pitching moment for control surface margin assessment. All QoIs are computed by the CFD solver and measured in the NTF experiment. Cp distributions provide additional spatial validation. Drag partitioning (skin friction vs pressure) flagged as unreliable for detailed accounting at this stage, appropriately limiting scope. Report.md Sections 1, 2, and 11.</t>
+          <t>QoIs are CL, CD, Cm, and surface Cp — directly required by the stated decisions (update lift-curve slope and zero-lift drag in performance workbook; bound pitching moment for control surface margin). These are standard aerodynamic integral outputs measured by the NTF balance and surface pressure instrumentation. Local Cp at spanwise stations provides spatial load distribution for aero-loads mapping. All QoIs are computable from the CFD and measured in the wind tunnel. Limitations clearly scoped: buffet margins, drag partitioning, and aeroelastic QoIs explicitly excluded from the current COU.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2738,12 +2753,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions (geometry, flow regime, operating point) match the intended use envelope</t>
+          <t>Validation conditions (geometry, flow regime, operating envelope) match the intended context of use</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation performed at M=0.85, Re=5M, α=2°–4° on the NASA CRM wing-body baseline geometry — directly matching the COU envelope (M≈0.85, Re≈5M, α∈[1°,4°], rigid geometry, fully turbulent). Gaps are explicitly documented: α=1° not validated (only sensitivity inferred); no Reynolds number sweep; single facility; no cross-code comparison; rigid-body assumption excludes elastic twist present in some WT datasets; extrapolation beyond α=4° not supported. These gaps are acknowledged and scope of applicability clearly bounded. Report.md Sections 1, 2, 11, and 12.</t>
+          <t>Validation performed on the exact CRM wing-body geometry at the exact COU conditions: M=0.85, Re=5M, α=2°–4° (COU is α=1°–4°; α=1° not covered in comparison set but lies within the monotonic regime). Same turbulence model, same rigid-body assumption, same fully turbulent condition as COU. Same mesh topology used in production runs as in validation. Gaps: (1) α=1° not included in validation comparison; (2) single facility only — NTF; (3) no Reynolds number sweep validation; (4) no Mach sensitivity validation beyond ±0.005; (5) rigid-body assumption creates systematic difference from real aircraft with elastic deformation; (6) no validation of unsteady or transition physics (explicitly excluded but represent gaps if COU were extended). Overall, validation is well-matched to the stated COU within its explicit scope.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2928,7 +2943,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The FUN3D v13.2 SA-neg RANS model on the C3 mesh is accepted for the stated context of use — bounding CL, CD, and Cm at M≈0.85, Re≈5M, α∈[1°,4°] for preliminary aero-loads and trim analyses — with the following conditions: (1) CD predictions carry a systematic underprediction of 6–10 counts growing with α; users must apply a +8-count empirical correction or substitute SST predictions as a sensitivity bracket before using CD in the performance workbook; (2) drag partitioning into skin friction and pressure drag must not be used for detailed drag accounting at this stage; (3) extrapolation beyond α=4° is not supported; (4) results are not valid for buffet margin, aeroelastic, high-lift, or unsteady analyses. Within these conditions, CL is within ±1.2% and Cm within 0.003 of NTF data, 95% uncertainty bands are quantified and traceable, and the workflow is reproducible. The model does not meet the bar for certification-grade drag accounting without further model-form and experimental coverage.</t>
+          <t>The FUN3D v13.2 SA-neg RANS model is accepted for the stated context of use: providing CL, CD, and Cm at M≈0.85, Re≈5M, α∈[1°,4°] for rigid CRM wing-body geometry to support performance workbook updates and preliminary pitching moment bounds. CL predictions are within ±1.2% of NTF data across all validated α values and fall within combined 95% uncertainty bands. Cm trend matches within 0.003 absolute. CD is systematically underpredicted (−1.4 to −9.6 counts), with the α=4° point slightly exceeding the ±9-count 95% band; the report recommends applying a +8-count empirical offset or substituting SST predictions as a sensitivity bracket, and this is accepted as a condition of use. Grid convergence, solver convergence, code verification, and input traceability are all adequately documented. Conditions of acceptance: (1) CD predictions must be used with the stated ±9-count uncertainty or with the recommended +8-count correction applied; (2) results must not be extrapolated beyond α=4°; (3) model must not be used for buffet, aeroelastic, drag-partitioning, or high-lift assessments without additional validation; (4) if drag accounting becomes critical, SST runs on C3 and/or unsteady simulations near α=4° should be conducted per recommendations in Section 13.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
